--- a/AAII_Financials/Quarterly/AEP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AEP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>AEP</t>
   </si>
@@ -656,539 +656,551 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5445000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6020000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5315300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6010400</v>
       </c>
-      <c r="G8" s="3">
-        <v>5086900</v>
-      </c>
       <c r="H8" s="3">
+        <v>5087000</v>
+      </c>
+      <c r="I8" s="3">
         <v>5463000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4696000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5420100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4579200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5025700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4577200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5341700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4372500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4690900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4881100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5526100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4639700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4592600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4061400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4623000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3826500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4281100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3610600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4066400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3494000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3747500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3616000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4315000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3573600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4056800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3801100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4333100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4013200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4048300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3810400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4104700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3576500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3933300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3790100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4652200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2861000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3279000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2903400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3183100</v>
       </c>
-      <c r="G9" s="3">
-        <v>2469700</v>
-      </c>
       <c r="H9" s="3">
+        <v>2469000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2924000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2386400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2808700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2537300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2655600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2763400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2802200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2395800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2703700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3059800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3207000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2510700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2447900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2298100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2454500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1955200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2428000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2034700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2140900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1774300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2002600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2222200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2391100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2097700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2352700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2308600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2767700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2419800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2517000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2213700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2338500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2098000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2309800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2549100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2711500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2584000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2741000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2411900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2827300</v>
       </c>
-      <c r="G10" s="3">
-        <v>2617200</v>
-      </c>
       <c r="H10" s="3">
+        <v>2618000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2539000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2309600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2611400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2041900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2370100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1813800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2539500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1976700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1987200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1821300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2319100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2129000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2144700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1763300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2168500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1871300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1853100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1575900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1925500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1719700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1744900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1393800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1923900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1475900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1704100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1492500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1565400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1593400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1531300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1596700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1766200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1478500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1623500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1241000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1940700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,8 +1243,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1353,8 +1366,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,19 +1491,22 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>31000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>66000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1495,47 +1514,47 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>142500</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>66300</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>112000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>123900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>182400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-47500</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11600</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1543,11 +1562,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1555,11 +1574,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>156400</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1567,12 +1586,12 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>70600</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1580,147 +1599,153 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>87100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-215300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>2900</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>2264900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>910000</v>
+      </c>
+      <c r="E15" s="3">
         <v>907000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>813900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>879600</v>
       </c>
-      <c r="G15" s="3">
-        <v>853100</v>
-      </c>
       <c r="H15" s="3">
+        <v>854000</v>
+      </c>
+      <c r="I15" s="3">
         <v>833000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>828300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>852700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>821900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>787100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>781000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>792300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>741600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>775500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>786000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>821800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>802600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>792400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>721800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>700300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>707300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>696300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>686500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>644600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>679500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>672200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>640900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>645200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>622600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>605800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>591100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>602600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>553200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>539700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>511300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>518500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>485500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>481900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>412100</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>539300</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1785,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4179000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4591000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4101100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4454600</v>
       </c>
-      <c r="G17" s="3">
-        <v>3653200</v>
-      </c>
       <c r="H17" s="3">
+        <v>3653000</v>
+      </c>
+      <c r="I17" s="3">
         <v>4144000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3602500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4022100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3715400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3808000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3832300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3933200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3442600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3818600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4321000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4596000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3635300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3604500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3377700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3515600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3016600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3470800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3040400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3123200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2771300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2995900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3321300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3356800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3022600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3250000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3664500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3256200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3342300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3079500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3129600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2843200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2836200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3214200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5780100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1429000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1214200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1555800</v>
       </c>
-      <c r="G18" s="3">
-        <v>1433700</v>
-      </c>
       <c r="H18" s="3">
+        <v>1434000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1319000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1093500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1398000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>863800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1217700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>744900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1408500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>929900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>872300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>560100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>930100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1004400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>988100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>683700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1107400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>809900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>810300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>570200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>943200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>722700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>751600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>294700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>958200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>551000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>788400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>551100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>668600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>757000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>706000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>730900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>975100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>733300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1097100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>575900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-1127900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,618 +2080,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-101000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-105800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-91700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-93200</v>
-      </c>
       <c r="H20" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-103000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-94800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-93500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-81700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-71500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-84300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-74800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-66200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>64200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>52000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>34400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>49500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>62800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>51300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>71400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>35200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>44100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>38200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>33200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>36600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>38600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>28900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>38200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>37500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>19000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>28800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>19400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>13900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>14100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2294000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2437000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2133900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2527100</v>
       </c>
-      <c r="G21" s="3">
-        <v>2380000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2381000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2255000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2016600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2350700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1779200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2086500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1597400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2285100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1746300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1714000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1493200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1803900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1818500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1852900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1465800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1838200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1597700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1580600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1348400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1644600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1468500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1472500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>991300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1662100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1231200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1457900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1202300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1340600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1372300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1310600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1261200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1522400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1238200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1592900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1002100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>-584900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>585000</v>
+      </c>
+      <c r="E22" s="3">
         <v>552000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>533100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>508500</v>
       </c>
-      <c r="G22" s="3">
-        <v>489500</v>
-      </c>
       <c r="H22" s="3">
+        <v>489000</v>
+      </c>
+      <c r="I22" s="3">
         <v>495000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>463000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>498800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>465600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>435600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>460900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>470300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>460000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>415700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>355900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>325100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>299000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>282400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>267800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>266700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>268100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>256800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>251900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>246100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>258900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>260700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>244800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>232100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>200300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>226900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>211200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>225900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>211500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>203300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>195500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>203300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>201900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>200600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>182900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>199700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>799000</v>
+      </c>
+      <c r="E23" s="3">
         <v>947000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>720900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1139000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1037400</v>
-      </c>
       <c r="H23" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="I23" s="3">
         <v>927000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>724800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>999200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>349200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>863800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>289200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1022500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>544700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>410800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>268400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>657000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>739800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>755200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>452800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>849700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>604600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>604800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>389700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>732300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>507900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>516200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>88100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>759300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>387300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>600100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>368800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>480900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>583600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>540200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>554400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>800600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>550800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>910400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>407100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-1323900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E24" s="3">
         <v>44000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>115700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>138700</v>
       </c>
-      <c r="G24" s="3">
-        <v>-250900</v>
-      </c>
       <c r="H24" s="3">
+        <v>-251000</v>
+      </c>
+      <c r="I24" s="3">
         <v>125000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>58700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-141900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-48600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-85300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>54000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>52800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-70000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>69800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>61200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>54500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>30600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-43600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-54400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>44500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>32700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-80700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>72200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>102000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>198600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>264000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>190600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>343200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>60300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-534500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2828,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E26" s="3">
         <v>903000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>605200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000300</v>
       </c>
-      <c r="G26" s="3">
-        <v>1288300</v>
-      </c>
       <c r="H26" s="3">
+        <v>1289000</v>
+      </c>
+      <c r="I26" s="3">
         <v>802000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>666100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>961700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>342500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1005700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>337800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>958300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>516100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>353700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>673100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>685800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>702400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>522800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>779900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>543400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>550300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>359100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>733500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>495300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>469700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>131700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>718700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>441700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>555600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>336100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>561600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>511400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>438200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>355800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>536600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>360200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>567200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>346800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-789400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E27" s="3">
         <v>874000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>582000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>972000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1225800</v>
-      </c>
       <c r="H27" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="I27" s="3">
         <v>800000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>664000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>959600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>340300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1003100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>336200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>953700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>521200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>397000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>384300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>683700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>524500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>714700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>538900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>796000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>578200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>575000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>387500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>748600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>520800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>495200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>153500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>733500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>461300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>572800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>352500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>577600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>528400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>454400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>374000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>544700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>375000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>592200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>373400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-765800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3203,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,8 +3256,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -3214,11 +3274,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>48000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3238,11 +3298,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>10900</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3250,26 +3310,29 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>26700</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
         <v>0</v>
       </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3453,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,252 +3578,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E32" s="3">
         <v>101000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>105800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>91700</v>
       </c>
-      <c r="G32" s="3">
-        <v>93200</v>
-      </c>
       <c r="H32" s="3">
+        <v>93000</v>
+      </c>
+      <c r="I32" s="3">
         <v>103000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>94800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>93500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>81700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>71500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>84300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>74800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>66200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-64200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-52000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-34400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-49500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-62800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-51300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-71400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-35200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-44100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-38200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-33200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-36600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-38600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-28900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-38200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-38100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-37500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-28800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-19400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-13900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-14100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E33" s="3">
         <v>874000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>582000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>972000</v>
       </c>
-      <c r="G33" s="3">
-        <v>1225800</v>
-      </c>
       <c r="H33" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="I33" s="3">
         <v>800000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>664000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>959600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>340300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1003100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>336200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>953700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>521200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>397000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>384300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>683700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>524500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>714700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>538900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>796000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>578200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>575000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>435500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>748600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>520800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>495200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>153500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>733500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>461300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>572800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>363400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>577600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>528400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>454400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>400700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>544700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>375000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>592200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>373400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-765800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3953,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E35" s="3">
         <v>874000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>582000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>972000</v>
       </c>
-      <c r="G35" s="3">
-        <v>1225800</v>
-      </c>
       <c r="H35" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="I35" s="3">
         <v>800000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>664000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>959600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>340300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1003100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>336200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>953700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>521200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>397000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>384300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>683700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>524500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>714700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>538900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>796000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>578200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>575000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>435500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>748600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>520800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>495200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>153500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>733500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>461300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>572800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>363400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>577600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>528400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>454400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>400700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>544700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>375000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>592200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>373400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-765800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4255,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,740 +4300,759 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E41" s="3">
         <v>306000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>197000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1067700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>227300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>256800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>203000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>245800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>202500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>230700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>330100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>353300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>304900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>343500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>509400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>522200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>575300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>675600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>403400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1372700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>312700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>273200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>392700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>409700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>348800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1554600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>246800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>348800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>210500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>227700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>234100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>788300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>211200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>183400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>214600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>343900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>172400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>175000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>210500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>212200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E42" s="3">
         <v>210000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>220000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>225400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>212000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>206800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>215000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>228600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>225700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>217000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>214300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>211000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>202500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>194600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>187600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>202200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>192000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>208500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>220400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>218400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>221700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>199100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>200800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>209000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>192300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>185200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>202700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>198400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>175700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>168900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>159100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>164100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>163100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>167900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>161700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>310700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>317600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>275000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>331700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>279200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3313000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3184000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2952000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2892800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2908700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2684500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2670000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2722500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2822800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2504700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2603600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2725300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2577700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2445000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2444500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2279900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2187600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1798300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1858700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1997700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2004000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1846100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1779300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1638300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1590400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1499300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1482700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1556300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1617100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1674500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1717200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1876900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2063300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1638100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1660800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1553600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1539700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1567600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1758000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1928200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1789000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1665000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1622000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1585700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1622000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1582200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1715000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1685700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1763000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1770300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1879500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1720000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1681800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1457200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1350200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1134000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1102300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>966800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>989200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>978500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1188400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1271900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1310000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1267300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1279800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1195900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1169200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1051300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1034400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>946600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>921100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>847900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>915600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>922800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>953200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>916500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>982200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>955300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>967300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1024800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="E45" s="3">
         <v>840000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>778000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>788500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1016700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>846800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>925000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>636400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1182100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>703000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>731500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1350300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2918700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2967000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2365700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5181700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5313800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4618800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4337500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1217800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>879000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>668100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>668700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>813900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>861900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>857000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>976400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1011600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1023600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>897100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1082400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1015200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1216900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1222800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1262800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>943100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>797100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>643500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2766400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2504800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7134000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6623000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6052000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6860000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6321900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5936900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5789000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6020800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6652800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5849600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6082100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6736600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8041300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7798200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6775500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9320000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9371000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8268000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7809200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5785100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4605800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4258400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4351500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4338200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4273200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5292000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4077800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4166400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4061300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3914800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4113900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4692400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4570100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4135000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4253100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4067800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3809000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3616400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>6033900</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5949200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4991,8 +5095,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5069,130 +5173,136 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97315000</v>
+      </c>
+      <c r="E48" s="3">
         <v>95504000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>93035000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>88595900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>86917700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>84141500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82996000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80646700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>79441500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>78399000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>77313600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>76440200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>75315500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>73978500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>73984600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>70433100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>69338800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>68524200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>66579600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>67471000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>66462100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>65515000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>64768000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>63667400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>62839700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>61975600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>61095500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>59682700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>58219400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>57014000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>55099100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>53355700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>52441500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>51365100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>50261500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>48316500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>47227200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>46236300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>45639300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>44262200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5203,7 +5313,7 @@
         <v>53000</v>
       </c>
       <c r="F49" s="3">
-        <v>52500</v>
+        <v>53000</v>
       </c>
       <c r="G49" s="3">
         <v>52500</v>
@@ -5212,10 +5322,10 @@
         <v>52500</v>
       </c>
       <c r="I49" s="3">
+        <v>52500</v>
+      </c>
+      <c r="J49" s="3">
         <v>53000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>52500</v>
       </c>
       <c r="K49" s="3">
         <v>52500</v>
@@ -5313,8 +5423,11 @@
       <c r="AP49" s="3">
         <v>52500</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>52500</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5548,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5673,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8118000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6261000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7834000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6076400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5841700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5421600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6639000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4937500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4752600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4736700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5607400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4195300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4309900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4239400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12590700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11443800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12099000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12986700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13227400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>13028500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>13237800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13159200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11585200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10631200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10639400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10403900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10666500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9999100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10216800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9740700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9537300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9516800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9806000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10056900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10162000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>11528100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>11650400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>11823100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>11742000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>11178100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5923,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>121570000</v>
+      </c>
+      <c r="E54" s="3">
         <v>117776000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>114460000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>110253500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107778500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>104394600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103078000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>100119100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>99622600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97744600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96684000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>95125600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>96002100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>94517900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>93403300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>91249400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>90861300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>89831400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>87668700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>86337100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>84358200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>82985100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>80757200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>78689300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>77804800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>77724000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>75892300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>73900700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>72550000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>70722000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>68802800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>67617400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>66870100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>65609500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>64729100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>63964900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>62739100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>61728300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>63467700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>61442000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6095,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,740 +6140,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3969000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3148000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3429000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2806700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2714200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2380800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2638000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2265600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2331500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1990900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2032500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2258600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2433900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2269300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2670800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2240200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2198200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1694300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2054600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1597100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1641600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1703900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1709700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1659600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1628000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1593400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2085800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1766800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1689000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1497200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1874300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1579900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1635400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1449600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2065300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1537000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1268400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1116900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1688500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1340300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4960000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4370000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4861000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3154700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4805000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7617800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6034000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4583000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3852700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5043300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5552600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5621700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7364500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6643600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6598600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4105800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4606700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6388700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4767800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5025800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5586500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5178600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4565400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4308600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5214300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6573800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4494600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3899100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3594000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3448000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3608500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4146800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4870600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>5274900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3392300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3418600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>4606700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4050200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>4591000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3863100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4636000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4447000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4472000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3429800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3444900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3654300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3877000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3214600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3520500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3365100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3579200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2911900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3065800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3268300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3996900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5490400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5643100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5485600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5604300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3331100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3200500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3337600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3651600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3079000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3279700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3487500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3718700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2945300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3074100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3045400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3166000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2699500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2552300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2746900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2813700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2366400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2517100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2747400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3218500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14155000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12594000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13314000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9997600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11443300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14242300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13009000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10647600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10162700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10906600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11583600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11278100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13267100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12621700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13266300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11836400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12448000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13568600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12426700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9954000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10428600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10220100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9926700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9047200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10122000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11654700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10299100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8611200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8357100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7990600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8648800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8426200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9058300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>9471400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>8271300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7322000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8392200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7914500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>9498000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>7779400</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>48565000</v>
+      </c>
+      <c r="E61" s="3">
         <v>47438000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44831000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44735300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41819600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39312400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39964000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39638200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40487300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39146600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>38368900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37230100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>37295600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36775000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>34314600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33646600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32982700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30855700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31496800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32056500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>30659300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>30214800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28986400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28155500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26637700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>25783000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25376000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24807500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24421500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>23135600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>21648200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20869800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>19750600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18844900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>19419600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18362400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>16796900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>16722200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>17378400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>17319900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13809000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13272000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12850000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13059300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12755000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12919000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12721000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12999200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12784000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11954800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11633700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11762300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11909200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11917900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22085000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21180800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21070000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21313900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21021700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21726100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21575500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21274900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21024400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20779500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20634100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>20160600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>20195400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20346400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20222400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20252600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19337600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>19174100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>19215800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>18693900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>18712700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>20165700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>19695000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>19378300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>19171200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>18999700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7013,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7138,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7263,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>88281000</v>
+      </c>
+      <c r="E66" s="3">
         <v>84798000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>82242000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78774200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>76810100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77030600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>76092000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>73460300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73446900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71900900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>71398100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>69776000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>71878500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>70550100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69464000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>66897900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>66741700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>65985000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>65192200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>63985700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>62914600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61957000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>60161100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>58250900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>57728300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57942400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>56217200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>54113700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53232200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>51479500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49735000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>48570100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>48124200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>47109200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>46430200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>45886500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>44909500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>44039600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>46070700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>44120100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7435,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7558,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7683,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7808,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7933,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15989000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15795000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15441000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15369300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14896700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14169400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13869000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13700700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13211300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13338000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12800400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12929500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12405500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12313800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12345600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12389800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12108600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11985100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11667100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11523000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11098700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10892700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10687800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10621400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10221900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10038800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9900900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10095300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9694200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9565600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9325300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9293700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9023100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8801500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8626700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8532000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8276400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8194300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7892400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7809400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8183,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8308,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8433,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32079000</v>
+      </c>
+      <c r="E76" s="3">
         <v>31808000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31138000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>30389300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29871100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27320700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26944000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26617400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26135200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25803300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25246700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25309700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23901400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23738200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23939300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24351500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24119600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23846400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>22476500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22351400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21443600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21028100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20596100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20438400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20076500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19781600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19675100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19787000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19317800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19242500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19067800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19047300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18745900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18500300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18298900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>18078400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>17829600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>17688700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>17397000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>17321900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8683,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E81" s="3">
         <v>874000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>582000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>972000</v>
       </c>
-      <c r="G81" s="3">
-        <v>1225800</v>
-      </c>
       <c r="H81" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="I81" s="3">
         <v>800000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>664000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>959600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>340300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1003100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>336200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>953700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>521200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>397000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>384300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>683700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>524500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>714700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>538900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>796000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>578200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>575000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>435500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>748600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>520800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>495200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>153500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>733500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>461300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>572800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>363400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>577600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>528400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>454400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>400700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>544700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>375000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>592200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>373400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-765800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8985,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>854000</v>
+      </c>
+      <c r="E83" s="3">
         <v>833000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>790300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>852700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>821900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>787100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>714700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>792300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>741600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>775500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>738900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>821800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>802600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>792400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>868900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>821800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>779700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>815300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>745200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>721800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>725000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>719000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>706800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>666200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>701700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>695600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>658400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>670700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>643600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>630900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>622300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>633800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>577200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>567100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>511300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>518500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>485500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>481900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>412100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>539300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9233,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9358,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9483,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9608,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9733,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1519000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1813200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2459700</v>
       </c>
-      <c r="G89" s="3">
-        <v>1221100</v>
-      </c>
       <c r="H89" s="3">
+        <v>1221000</v>
+      </c>
+      <c r="I89" s="3">
         <v>1450000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1727100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2172700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1462000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1442200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1336500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1794100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1163800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>717800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>554800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1742500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1368500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1622200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>866900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1929100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1161100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-117200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>910700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1176000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1130500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>615700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>920200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1549100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>992500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>808300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1290600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1925800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1204600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>802200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1146200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1407200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>910200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>806800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1100800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1695200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9905,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3164000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3808000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4288600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2322300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-3289100</v>
-      </c>
       <c r="H91" s="3">
+        <v>-3288000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2136000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2903000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1878900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1592700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1795400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1679700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1712700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2031800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2237500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1932000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1634600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1488100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1717700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1613900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1302400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-55900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-36400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-23800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-34800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-35200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-2739000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-6304600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1149600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10153,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10278,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3033000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3569000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4189900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2401800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-3245300</v>
-      </c>
       <c r="H94" s="3">
+        <v>-3245000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2102000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2826500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1519800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1580400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1669300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1623200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-378000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2020300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2245200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1929300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1623500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1305800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2893200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1527700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1676400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1595600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1634200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1526600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1459700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1481600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1766000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1786900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1762600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2012200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1582800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1664900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1449800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1311100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1927800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1979800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1300900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1220500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>844800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1560400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1129000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,130 +10450,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E96" s="3">
         <v>520000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>510100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>499400</v>
       </c>
-      <c r="G96" s="3">
-        <v>498500</v>
-      </c>
       <c r="H96" s="3">
+        <v>499000</v>
+      </c>
+      <c r="I96" s="3">
         <v>500000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>495300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>470200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>467000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>465500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>464300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>429700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>429500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>428800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-432700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-409000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-404700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-398800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-396800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-376200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-374500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-372000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-369200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-351100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-340900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-363700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-348000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-333900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-334500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-333600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-333000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-308300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-308100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-306100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-316900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-290100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-293500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-291400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-291200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-276700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10698,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10823,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,130 +10948,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1239000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2121000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1537900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>770300</v>
       </c>
-      <c r="G100" s="3">
-        <v>2010800</v>
-      </c>
       <c r="H100" s="3">
+        <v>2011000</v>
+      </c>
+      <c r="I100" s="3">
         <v>698000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1046200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-601600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>84500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>129900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>258600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1359700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>813700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1364400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1353700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-162900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-167000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1545100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-314500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>814300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>470200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1637100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>590400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>242800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-815000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2388500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>809500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>313700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1046200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>693500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-119100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>74200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>177300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1029500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>709300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>65200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>307700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1687100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>457900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-600800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10872,8 +11120,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10950,126 +11198,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E102" s="3">
         <v>71000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-838800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>828200</v>
       </c>
-      <c r="G102" s="3">
-        <v>-13400</v>
-      </c>
       <c r="H102" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="I102" s="3">
         <v>46000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-53200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>51300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-97200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>56400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-42800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-163000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-43900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-104300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>274100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-975300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1067000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-114300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-40900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1166100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1238200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-57200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>100200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>26500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-81000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-493400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>550200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>70800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-96100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-124300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>171500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-35500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-34600</v>
       </c>
     </row>
